--- a/artfynd/S 1898-2025 artfynd.xlsx
+++ b/artfynd/S 1898-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY383"/>
+  <dimension ref="A1:AZ383"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104875193</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127784868</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -977,6 +992,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127784869</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1074,6 +1094,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127784870</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1171,6 +1196,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127784871</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1268,6 +1298,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127784872</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1365,6 +1400,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127784873</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1462,6 +1502,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127784902</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1582,6 +1627,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111962401</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1693,6 +1743,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127009893</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1804,6 +1859,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127045337</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1920,6 +1980,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134454916</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2017,6 +2082,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127085224</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2114,6 +2184,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127085277</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2222,6 +2297,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104711053</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2333,6 +2413,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104719045</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2444,6 +2529,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104745905</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2552,6 +2642,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104765281</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2663,6 +2758,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104872813</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2774,6 +2874,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104957961</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2882,6 +2987,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109578959</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2990,6 +3100,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109580930</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3101,6 +3216,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109585186</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3209,6 +3329,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110210683</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3306,6 +3431,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121216498</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3403,6 +3533,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121467146</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3504,6 +3639,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121514534</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3615,6 +3755,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121526891</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3731,6 +3876,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126699507</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3857,6 +4007,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126702981</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3973,6 +4128,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126705789</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4080,6 +4240,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127011342</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4187,6 +4352,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127011469</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4294,6 +4464,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127015415</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4391,6 +4566,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127085123</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4498,6 +4678,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127155828</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4600,6 +4785,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127784855</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4697,6 +4887,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127784881</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4794,6 +4989,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127784882</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4891,6 +5091,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127784916</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4988,6 +5193,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127784981</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5085,6 +5295,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127784982</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5196,6 +5411,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129174357</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5307,6 +5527,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104875099</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5418,6 +5643,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121533633</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5515,6 +5745,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127784895</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5626,6 +5861,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104710073</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5737,6 +5977,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104872774</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5845,6 +6090,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111966368</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5969,6 +6219,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115536027</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6085,6 +6340,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121467155</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6196,6 +6456,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121467159</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6293,6 +6558,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127085213</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6390,6 +6660,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127085217</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6516,6 +6791,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126680630</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6613,6 +6893,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127784978</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6732,6 +7017,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129626514</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6829,6 +7119,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127784883</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6953,6 +7248,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123786213</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7060,6 +7360,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129174569</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7179,6 +7484,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129175223</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7287,6 +7597,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111958998</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7395,6 +7710,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111958864</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7506,6 +7826,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129174415</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7617,6 +7942,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104743949</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7737,6 +8067,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110209534</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7848,6 +8183,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121467157</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7964,6 +8304,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121520970</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8080,6 +8425,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121526747</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8191,6 +8541,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126412703</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8332,6 +8687,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126703143</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8439,6 +8799,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127030834</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8536,6 +8901,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127085098</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8633,6 +9003,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127085099</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8730,6 +9105,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127784852</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8827,6 +9207,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127784853</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8924,6 +9309,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127784874</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9021,6 +9411,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127784875</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9118,6 +9513,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127784876</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9215,6 +9615,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127784877</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9326,6 +9731,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129621711</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9433,6 +9843,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120252919</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9557,6 +9972,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120788315</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9672,6 +10092,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120788329</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9783,6 +10208,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129174923</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9894,6 +10324,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104719221</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10010,6 +10445,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104743081</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10126,6 +10566,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104743217</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10237,6 +10682,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104744427</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10348,6 +10798,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104744515</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10459,6 +10914,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104744689</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10575,6 +11035,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104744738</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10691,6 +11156,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104755547</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10802,6 +11272,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104755741</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10910,6 +11385,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104755745</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11021,6 +11501,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104756077</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11137,6 +11622,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104756517</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11248,6 +11738,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104874644</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11359,6 +11854,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104875371</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11475,6 +11975,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104913325</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11586,6 +12091,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104914082</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11687,6 +12197,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105028752</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11798,6 +12313,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105227333</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11909,6 +12429,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106169069</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12017,6 +12542,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106169152</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12128,6 +12658,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106169290</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12244,6 +12779,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106169489</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12352,6 +12892,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106982293</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12463,6 +13008,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106982394</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12571,6 +13121,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106982664</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12668,6 +13223,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107243502</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12765,6 +13325,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107243504</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12862,6 +13427,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107243506</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12959,6 +13529,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107243507</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -13060,6 +13635,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107711228</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13168,6 +13748,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109574071</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -13276,6 +13861,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109575930</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -13384,6 +13974,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109582589</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -13508,6 +14103,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111765239</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13616,6 +14216,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111959882</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13724,6 +14329,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111960194</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13832,6 +14442,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111960268</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13948,6 +14563,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111962428</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -14061,6 +14681,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111963563</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -14172,6 +14797,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121467160</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -14296,6 +14926,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124628366</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -14420,6 +15055,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124630777</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -14527,6 +15167,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124636625</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -14643,6 +15288,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126416537</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -14755,6 +15405,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127026278</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -14867,6 +15522,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127033214</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -14979,6 +15639,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127033281</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -15091,6 +15756,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127033292</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -15193,6 +15863,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127085318</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -15290,6 +15965,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127085320</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -15387,6 +16067,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127085321</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -15484,6 +16169,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127085322</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -15581,6 +16271,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127085323</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -15678,6 +16373,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127085325</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -15775,6 +16475,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127085326</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -15872,6 +16577,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127085327</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -15969,6 +16679,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127085328</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -16066,6 +16781,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127085329</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -16163,6 +16883,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127085330</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -16260,6 +16985,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127085332</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -16357,6 +17087,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127085333</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -16454,6 +17189,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127085358</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -16551,6 +17291,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127085359</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -16648,6 +17393,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127085360</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -16745,6 +17495,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127085361</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -16842,6 +17597,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127085362</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -16939,6 +17699,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127085363</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -17046,6 +17811,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127154240</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -17153,6 +17923,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127154613</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -17260,6 +18035,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127155444</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -17367,6 +18147,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127155536</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -17474,6 +18259,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127155628</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -17581,6 +18371,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127155638</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -17688,6 +18483,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127155642</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -17795,6 +18595,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127155653</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -17902,6 +18707,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127173747</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -18009,6 +18819,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127173858</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -18106,6 +18921,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127784864</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -18203,6 +19023,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127784896</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -18300,6 +19125,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127784897</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -18397,6 +19227,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127784898</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -18494,6 +19329,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127784899</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -18591,6 +19431,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127784900</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -18688,6 +19533,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127784901</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -18795,6 +19645,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129620875</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -18902,6 +19757,11 @@
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129621067</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -19013,6 +19873,11 @@
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127025327</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -19124,6 +19989,11 @@
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127026427</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -19231,6 +20101,11 @@
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127029551</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -19342,6 +20217,11 @@
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127031298</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -19453,6 +20333,11 @@
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127031347</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -19555,6 +20440,11 @@
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127784885</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -19675,6 +20565,11 @@
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104709827</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -19790,6 +20685,11 @@
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104714993</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -19905,6 +20805,11 @@
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104720235</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -20021,6 +20926,11 @@
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104744046</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -20132,6 +21042,11 @@
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104744732</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -20243,6 +21158,11 @@
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104755065</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -20354,6 +21274,11 @@
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104755848</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -20470,6 +21395,11 @@
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104875190</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -20583,6 +21513,11 @@
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104875435</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -20696,6 +21631,11 @@
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104875452</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -20804,6 +21744,11 @@
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104998712</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -20912,6 +21857,11 @@
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105008784</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -21020,6 +21970,11 @@
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105227068</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -21131,6 +22086,11 @@
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106783968</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -21237,6 +22197,11 @@
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106832558</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -21352,6 +22317,11 @@
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109580238</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -21459,6 +22429,11 @@
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115925128</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -21566,6 +22541,11 @@
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115928571</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -21677,6 +22657,11 @@
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115929159</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -21789,6 +22774,11 @@
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124627632</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -21909,6 +22899,11 @@
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124631094</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -22033,6 +23028,11 @@
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124631653</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -22148,6 +23148,11 @@
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124635929</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -22263,6 +23268,11 @@
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126258868</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -22387,6 +23397,11 @@
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126258881</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -22507,6 +23522,11 @@
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126414466</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -22627,6 +23647,11 @@
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126416448</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -22734,6 +23759,11 @@
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127011674</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -22841,6 +23871,11 @@
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127015008</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -22948,6 +23983,11 @@
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127082605</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -23055,6 +24095,11 @@
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127084217</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -23157,6 +24202,11 @@
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127085178</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -23259,6 +24309,11 @@
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127085179</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -23361,6 +24416,11 @@
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127085189</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -23463,6 +24523,11 @@
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127085190</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -23565,6 +24630,11 @@
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127085191</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -23667,6 +24737,11 @@
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127784887</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -23787,6 +24862,11 @@
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129174190</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -23894,6 +24974,11 @@
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>
+      <c r="AZ217" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129616543</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -24001,6 +25086,11 @@
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
+      <c r="AZ218" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129617089</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -24113,6 +25203,11 @@
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129620453</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -24220,6 +25315,11 @@
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127014855</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -24332,6 +25432,11 @@
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127084135</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -24452,6 +25557,11 @@
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124628165</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -24568,6 +25678,11 @@
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
+      <c r="AZ223" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106701446</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -24684,6 +25799,11 @@
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106709944</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -24800,6 +25920,11 @@
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106783406</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -24928,6 +26053,11 @@
         </is>
       </c>
       <c r="AY226" t="inlineStr"/>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106806348</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -25056,6 +26186,11 @@
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106954204</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -25175,6 +26310,11 @@
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
+      <c r="AZ228" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107189128</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -25281,6 +26421,11 @@
         </is>
       </c>
       <c r="AY229" t="inlineStr"/>
+      <c r="AZ229" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115536805</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -25407,6 +26552,11 @@
         </is>
       </c>
       <c r="AY230" t="inlineStr"/>
+      <c r="AZ230" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121527373</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -25527,6 +26677,11 @@
         </is>
       </c>
       <c r="AY231" t="inlineStr"/>
+      <c r="AZ231" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123769986</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -25647,6 +26802,11 @@
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
+      <c r="AZ232" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126252401</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -25767,6 +26927,11 @@
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
+      <c r="AZ233" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126707889</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -25878,6 +27043,11 @@
         </is>
       </c>
       <c r="AY234" t="inlineStr"/>
+      <c r="AZ234" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127083556</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -25985,6 +27155,11 @@
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
+      <c r="AZ235" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127085141</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -26092,6 +27267,11 @@
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
+      <c r="AZ236" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127085143</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -26199,6 +27379,11 @@
         </is>
       </c>
       <c r="AY237" t="inlineStr"/>
+      <c r="AZ237" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127085153</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -26310,6 +27495,11 @@
         </is>
       </c>
       <c r="AY238" t="inlineStr"/>
+      <c r="AZ238" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127108117</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -26425,6 +27615,11 @@
         </is>
       </c>
       <c r="AY239" t="inlineStr"/>
+      <c r="AZ239" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129171329</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -26540,6 +27735,11 @@
         </is>
       </c>
       <c r="AY240" t="inlineStr"/>
+      <c r="AZ240" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129615940</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -26647,6 +27847,11 @@
         </is>
       </c>
       <c r="AY241" t="inlineStr"/>
+      <c r="AZ241" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134453847</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -26766,6 +27971,11 @@
         </is>
       </c>
       <c r="AY242" t="inlineStr"/>
+      <c r="AZ242" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107184165</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -26890,6 +28100,11 @@
         </is>
       </c>
       <c r="AY243" t="inlineStr"/>
+      <c r="AZ243" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110208385</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -27014,6 +28229,11 @@
         </is>
       </c>
       <c r="AY244" t="inlineStr"/>
+      <c r="AZ244" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110256438</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -27134,6 +28354,11 @@
         </is>
       </c>
       <c r="AY245" t="inlineStr"/>
+      <c r="AZ245" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123769974</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -27258,6 +28483,11 @@
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
+      <c r="AZ246" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123769975</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -27378,6 +28608,11 @@
         </is>
       </c>
       <c r="AY247" t="inlineStr"/>
+      <c r="AZ247" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123769988</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -27498,6 +28733,11 @@
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
+      <c r="AZ248" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123769992</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -27618,6 +28858,11 @@
         </is>
       </c>
       <c r="AY249" t="inlineStr"/>
+      <c r="AZ249" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123777348</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -27742,6 +28987,11 @@
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
+      <c r="AZ250" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123777350</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -27866,6 +29116,11 @@
         </is>
       </c>
       <c r="AY251" t="inlineStr"/>
+      <c r="AZ251" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123777354</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -27990,6 +29245,11 @@
         </is>
       </c>
       <c r="AY252" t="inlineStr"/>
+      <c r="AZ252" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123777355</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -28110,6 +29370,11 @@
         </is>
       </c>
       <c r="AY253" t="inlineStr"/>
+      <c r="AZ253" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123777358</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -28230,6 +29495,11 @@
         </is>
       </c>
       <c r="AY254" t="inlineStr"/>
+      <c r="AZ254" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123777359</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -28350,6 +29620,11 @@
         </is>
       </c>
       <c r="AY255" t="inlineStr"/>
+      <c r="AZ255" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123777364</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -28470,6 +29745,11 @@
         </is>
       </c>
       <c r="AY256" t="inlineStr"/>
+      <c r="AZ256" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123777369</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -28594,6 +29874,11 @@
         </is>
       </c>
       <c r="AY257" t="inlineStr"/>
+      <c r="AZ257" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123777370</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -28714,6 +29999,11 @@
         </is>
       </c>
       <c r="AY258" t="inlineStr"/>
+      <c r="AZ258" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123777372</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -28834,6 +30124,11 @@
         </is>
       </c>
       <c r="AY259" t="inlineStr"/>
+      <c r="AZ259" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123777374</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -28954,6 +30249,11 @@
         </is>
       </c>
       <c r="AY260" t="inlineStr"/>
+      <c r="AZ260" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123777375</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -29074,6 +30374,11 @@
         </is>
       </c>
       <c r="AY261" t="inlineStr"/>
+      <c r="AZ261" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123777376</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -29194,6 +30499,11 @@
         </is>
       </c>
       <c r="AY262" t="inlineStr"/>
+      <c r="AZ262" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123777377</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -29314,6 +30624,11 @@
         </is>
       </c>
       <c r="AY263" t="inlineStr"/>
+      <c r="AZ263" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123777379</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -29434,6 +30749,11 @@
         </is>
       </c>
       <c r="AY264" t="inlineStr"/>
+      <c r="AZ264" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123786209</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -29558,6 +30878,11 @@
         </is>
       </c>
       <c r="AY265" t="inlineStr"/>
+      <c r="AZ265" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123786210</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -29678,6 +31003,11 @@
         </is>
       </c>
       <c r="AY266" t="inlineStr"/>
+      <c r="AZ266" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123786212</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -29802,6 +31132,11 @@
         </is>
       </c>
       <c r="AY267" t="inlineStr"/>
+      <c r="AZ267" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123786214</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -29922,6 +31257,11 @@
         </is>
       </c>
       <c r="AY268" t="inlineStr"/>
+      <c r="AZ268" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123786215</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -30050,6 +31390,11 @@
         </is>
       </c>
       <c r="AY269" t="inlineStr"/>
+      <c r="AZ269" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123786219</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -30178,6 +31523,11 @@
         </is>
       </c>
       <c r="AY270" t="inlineStr"/>
+      <c r="AZ270" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123786220</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -30302,6 +31652,11 @@
         </is>
       </c>
       <c r="AY271" t="inlineStr"/>
+      <c r="AZ271" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123786221</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -30426,6 +31781,11 @@
         </is>
       </c>
       <c r="AY272" t="inlineStr"/>
+      <c r="AZ272" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123786222</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -30550,6 +31910,11 @@
         </is>
       </c>
       <c r="AY273" t="inlineStr"/>
+      <c r="AZ273" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123786223</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -30674,6 +32039,11 @@
         </is>
       </c>
       <c r="AY274" t="inlineStr"/>
+      <c r="AZ274" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123786225</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -30785,6 +32155,11 @@
         </is>
       </c>
       <c r="AY275" t="inlineStr"/>
+      <c r="AZ275" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124626973</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -30900,6 +32275,11 @@
         </is>
       </c>
       <c r="AY276" t="inlineStr"/>
+      <c r="AZ276" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124627337</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -31007,6 +32387,11 @@
         </is>
       </c>
       <c r="AY277" t="inlineStr"/>
+      <c r="AZ277" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124628098</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -31122,6 +32507,11 @@
         </is>
       </c>
       <c r="AY278" t="inlineStr"/>
+      <c r="AZ278" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124628697</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -31234,6 +32624,11 @@
         </is>
       </c>
       <c r="AY279" t="inlineStr"/>
+      <c r="AZ279" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124629814</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -31349,6 +32744,11 @@
         </is>
       </c>
       <c r="AY280" t="inlineStr"/>
+      <c r="AZ280" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124630435</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -31464,6 +32864,11 @@
         </is>
       </c>
       <c r="AY281" t="inlineStr"/>
+      <c r="AZ281" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124636360</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -31574,6 +32979,11 @@
         </is>
       </c>
       <c r="AY282" t="inlineStr"/>
+      <c r="AZ282" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124775855</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -31694,6 +33104,11 @@
         </is>
       </c>
       <c r="AY283" t="inlineStr"/>
+      <c r="AZ283" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126252382</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -31818,6 +33233,11 @@
         </is>
       </c>
       <c r="AY284" t="inlineStr"/>
+      <c r="AZ284" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126252385</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -31938,6 +33358,11 @@
         </is>
       </c>
       <c r="AY285" t="inlineStr"/>
+      <c r="AZ285" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126252386</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -32058,6 +33483,11 @@
         </is>
       </c>
       <c r="AY286" t="inlineStr"/>
+      <c r="AZ286" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126252387</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -32178,6 +33608,11 @@
         </is>
       </c>
       <c r="AY287" t="inlineStr"/>
+      <c r="AZ287" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126252391</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -32298,6 +33733,11 @@
         </is>
       </c>
       <c r="AY288" t="inlineStr"/>
+      <c r="AZ288" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126252392</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -32422,6 +33862,11 @@
         </is>
       </c>
       <c r="AY289" t="inlineStr"/>
+      <c r="AZ289" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126252402</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -32542,6 +33987,11 @@
         </is>
       </c>
       <c r="AY290" t="inlineStr"/>
+      <c r="AZ290" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126688750</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -32662,6 +34112,11 @@
         </is>
       </c>
       <c r="AY291" t="inlineStr"/>
+      <c r="AZ291" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126688757</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -32782,6 +34237,11 @@
         </is>
       </c>
       <c r="AY292" t="inlineStr"/>
+      <c r="AZ292" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126703547</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -32891,6 +34351,11 @@
         </is>
       </c>
       <c r="AY293" t="inlineStr"/>
+      <c r="AZ293" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127085162</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -33006,6 +34471,11 @@
         </is>
       </c>
       <c r="AY294" t="inlineStr"/>
+      <c r="AZ294" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127108147</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -33126,6 +34596,11 @@
         </is>
       </c>
       <c r="AY295" t="inlineStr"/>
+      <c r="AZ295" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129175048</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -33241,6 +34716,11 @@
         </is>
       </c>
       <c r="AY296" t="inlineStr"/>
+      <c r="AZ296" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129615995</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -33357,6 +34837,11 @@
         </is>
       </c>
       <c r="AY297" t="inlineStr"/>
+      <c r="AZ297" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129618459</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -33464,6 +34949,11 @@
         </is>
       </c>
       <c r="AY298" t="inlineStr"/>
+      <c r="AZ298" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129620586</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -33577,6 +35067,11 @@
         </is>
       </c>
       <c r="AY299" t="inlineStr"/>
+      <c r="AZ299" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109574015</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -33690,6 +35185,11 @@
         </is>
       </c>
       <c r="AY300" t="inlineStr"/>
+      <c r="AZ300" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109579875</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -33802,6 +35302,11 @@
         </is>
       </c>
       <c r="AY301" t="inlineStr"/>
+      <c r="AZ301" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127033454</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -33919,6 +35424,11 @@
         </is>
       </c>
       <c r="AY302" t="inlineStr"/>
+      <c r="AZ302" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127047724</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -34036,6 +35546,11 @@
         </is>
       </c>
       <c r="AY303" t="inlineStr"/>
+      <c r="AZ303" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127047835</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -34153,6 +35668,11 @@
         </is>
       </c>
       <c r="AY304" t="inlineStr"/>
+      <c r="AZ304" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127048049</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -34270,6 +35790,11 @@
         </is>
       </c>
       <c r="AY305" t="inlineStr"/>
+      <c r="AZ305" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127048206</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -34372,6 +35897,11 @@
         </is>
       </c>
       <c r="AY306" t="inlineStr"/>
+      <c r="AZ306" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127085165</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -34474,6 +36004,11 @@
         </is>
       </c>
       <c r="AY307" t="inlineStr"/>
+      <c r="AZ307" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127085166</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -34576,6 +36111,11 @@
         </is>
       </c>
       <c r="AY308" t="inlineStr"/>
+      <c r="AZ308" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127085167</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -34688,6 +36228,11 @@
         </is>
       </c>
       <c r="AY309" t="inlineStr"/>
+      <c r="AZ309" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127151243</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -34800,6 +36345,11 @@
         </is>
       </c>
       <c r="AY310" t="inlineStr"/>
+      <c r="AZ310" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127154189</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -34917,6 +36467,11 @@
         </is>
       </c>
       <c r="AY311" t="inlineStr"/>
+      <c r="AZ311" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127158677</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -35024,6 +36579,11 @@
         </is>
       </c>
       <c r="AY312" t="inlineStr"/>
+      <c r="AZ312" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127784884</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -35137,6 +36697,11 @@
         </is>
       </c>
       <c r="AY313" t="inlineStr"/>
+      <c r="AZ313" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104718188</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -35245,6 +36810,11 @@
         </is>
       </c>
       <c r="AY314" t="inlineStr"/>
+      <c r="AZ314" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104756507</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -35353,6 +36923,11 @@
         </is>
       </c>
       <c r="AY315" t="inlineStr"/>
+      <c r="AZ315" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106212374</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -35466,6 +37041,11 @@
         </is>
       </c>
       <c r="AY316" t="inlineStr"/>
+      <c r="AZ316" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109579783</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -35587,6 +37167,11 @@
         </is>
       </c>
       <c r="AY317" t="inlineStr"/>
+      <c r="AZ317" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111765246</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -35700,6 +37285,11 @@
         </is>
       </c>
       <c r="AY318" t="inlineStr"/>
+      <c r="AZ318" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115535311</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -35803,6 +37393,11 @@
         </is>
       </c>
       <c r="AY319" t="inlineStr"/>
+      <c r="AZ319" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121467162</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -35910,6 +37505,11 @@
         </is>
       </c>
       <c r="AY320" t="inlineStr"/>
+      <c r="AZ320" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124629152</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -36028,6 +37628,11 @@
         </is>
       </c>
       <c r="AY321" t="inlineStr"/>
+      <c r="AZ321" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126411537</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -36146,6 +37751,11 @@
         </is>
       </c>
       <c r="AY322" t="inlineStr"/>
+      <c r="AZ322" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126703152</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -36258,6 +37868,11 @@
         </is>
       </c>
       <c r="AY323" t="inlineStr"/>
+      <c r="AZ323" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127013462</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -36376,6 +37991,11 @@
         </is>
       </c>
       <c r="AY324" t="inlineStr"/>
+      <c r="AZ324" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127031696</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -36488,6 +38108,11 @@
         </is>
       </c>
       <c r="AY325" t="inlineStr"/>
+      <c r="AZ325" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127033428</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -36605,6 +38230,11 @@
         </is>
       </c>
       <c r="AY326" t="inlineStr"/>
+      <c r="AZ326" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127047707</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -36722,6 +38352,11 @@
         </is>
       </c>
       <c r="AY327" t="inlineStr"/>
+      <c r="AZ327" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127047841</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -36839,6 +38474,11 @@
         </is>
       </c>
       <c r="AY328" t="inlineStr"/>
+      <c r="AZ328" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127048044</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -36956,6 +38596,11 @@
         </is>
       </c>
       <c r="AY329" t="inlineStr"/>
+      <c r="AZ329" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127048201</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -37058,6 +38703,11 @@
         </is>
       </c>
       <c r="AY330" t="inlineStr"/>
+      <c r="AZ330" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127085455</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -37170,6 +38820,11 @@
         </is>
       </c>
       <c r="AY331" t="inlineStr"/>
+      <c r="AZ331" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127154592</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
@@ -37277,6 +38932,11 @@
         </is>
       </c>
       <c r="AY332" t="inlineStr"/>
+      <c r="AZ332" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129170584</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
@@ -37390,6 +39050,11 @@
         </is>
       </c>
       <c r="AY333" t="inlineStr"/>
+      <c r="AZ333" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133343553</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -37512,6 +39177,11 @@
         </is>
       </c>
       <c r="AY334" t="inlineStr"/>
+      <c r="AZ334" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134624221</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -37624,6 +39294,11 @@
         </is>
       </c>
       <c r="AY335" t="inlineStr"/>
+      <c r="AZ335" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127152893</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -37744,6 +39419,11 @@
         </is>
       </c>
       <c r="AY336" t="inlineStr"/>
+      <c r="AZ336" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123767919</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -37860,6 +39540,11 @@
         </is>
       </c>
       <c r="AY337" t="inlineStr"/>
+      <c r="AZ337" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126688753</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -37980,6 +39665,11 @@
         </is>
       </c>
       <c r="AY338" t="inlineStr"/>
+      <c r="AZ338" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126688754</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
@@ -38087,6 +39777,11 @@
         </is>
       </c>
       <c r="AY339" t="inlineStr"/>
+      <c r="AZ339" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127014946</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
@@ -38202,6 +39897,11 @@
         </is>
       </c>
       <c r="AY340" t="inlineStr"/>
+      <c r="AZ340" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124633056</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
@@ -38309,6 +40009,11 @@
         </is>
       </c>
       <c r="AY341" t="inlineStr"/>
+      <c r="AZ341" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126413105</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
@@ -38416,6 +40121,11 @@
         </is>
       </c>
       <c r="AY342" t="inlineStr"/>
+      <c r="AZ342" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127014469</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
@@ -38523,6 +40233,11 @@
         </is>
       </c>
       <c r="AY343" t="inlineStr"/>
+      <c r="AZ343" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127014933</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
@@ -38644,6 +40359,11 @@
         </is>
       </c>
       <c r="AY344" t="inlineStr"/>
+      <c r="AZ344" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104872335</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
@@ -38754,6 +40474,11 @@
         </is>
       </c>
       <c r="AY345" t="inlineStr"/>
+      <c r="AZ345" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105090857</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
@@ -38877,6 +40602,11 @@
         </is>
       </c>
       <c r="AY346" t="inlineStr"/>
+      <c r="AZ346" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106954216</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
@@ -38990,6 +40720,11 @@
         </is>
       </c>
       <c r="AY347" t="inlineStr"/>
+      <c r="AZ347" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109602181</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
@@ -39110,6 +40845,11 @@
         </is>
       </c>
       <c r="AY348" t="inlineStr"/>
+      <c r="AZ348" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120515014</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
@@ -39226,6 +40966,11 @@
         </is>
       </c>
       <c r="AY349" t="inlineStr"/>
+      <c r="AZ349" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121401512</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
@@ -39333,6 +41078,11 @@
         </is>
       </c>
       <c r="AY350" t="inlineStr"/>
+      <c r="AZ350" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127014013</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
@@ -39430,6 +41180,11 @@
         </is>
       </c>
       <c r="AY351" t="inlineStr"/>
+      <c r="AZ351" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127784860</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
@@ -39550,6 +41305,11 @@
         </is>
       </c>
       <c r="AY352" t="inlineStr"/>
+      <c r="AZ352" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124629179</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
@@ -39663,6 +41423,11 @@
         </is>
       </c>
       <c r="AY353" t="inlineStr"/>
+      <c r="AZ353" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104914262</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
@@ -39785,6 +41550,11 @@
         </is>
       </c>
       <c r="AY354" t="inlineStr"/>
+      <c r="AZ354" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109573919</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
@@ -39902,6 +41672,11 @@
         </is>
       </c>
       <c r="AY355" t="inlineStr"/>
+      <c r="AZ355" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127209685</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
@@ -40004,6 +41779,11 @@
         </is>
       </c>
       <c r="AY356" t="inlineStr"/>
+      <c r="AZ356" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127784849</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
@@ -40112,6 +41892,11 @@
         </is>
       </c>
       <c r="AY357" t="inlineStr"/>
+      <c r="AZ357" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104755491</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
@@ -40224,6 +42009,11 @@
         </is>
       </c>
       <c r="AY358" t="inlineStr"/>
+      <c r="AZ358" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104776715</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
@@ -40321,6 +42111,11 @@
         </is>
       </c>
       <c r="AY359" t="inlineStr"/>
+      <c r="AZ359" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107243503</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
@@ -40429,6 +42224,11 @@
         </is>
       </c>
       <c r="AY360" t="inlineStr"/>
+      <c r="AZ360" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110255587</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
@@ -40553,6 +42353,11 @@
         </is>
       </c>
       <c r="AY361" t="inlineStr"/>
+      <c r="AZ361" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123767910</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
@@ -40677,6 +42482,11 @@
         </is>
       </c>
       <c r="AY362" t="inlineStr"/>
+      <c r="AZ362" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123767921</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
@@ -40801,6 +42611,11 @@
         </is>
       </c>
       <c r="AY363" t="inlineStr"/>
+      <c r="AZ363" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123767922</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
@@ -40921,6 +42736,11 @@
         </is>
       </c>
       <c r="AY364" t="inlineStr"/>
+      <c r="AZ364" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123789075</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
@@ -41037,6 +42857,11 @@
         </is>
       </c>
       <c r="AY365" t="inlineStr"/>
+      <c r="AZ365" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126688587</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
@@ -41163,6 +42988,11 @@
         </is>
       </c>
       <c r="AY366" t="inlineStr"/>
+      <c r="AZ366" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110428414</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
@@ -41289,6 +43119,11 @@
         </is>
       </c>
       <c r="AY367" t="inlineStr"/>
+      <c r="AZ367" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124643526</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
@@ -41414,6 +43249,11 @@
         </is>
       </c>
       <c r="AY368" t="inlineStr"/>
+      <c r="AZ368" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126258662</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
@@ -41522,6 +43362,11 @@
         </is>
       </c>
       <c r="AY369" t="inlineStr"/>
+      <c r="AZ369" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104744866</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
@@ -41620,6 +43465,11 @@
         </is>
       </c>
       <c r="AY370" t="inlineStr"/>
+      <c r="AZ370" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111783083</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
@@ -41728,6 +43578,11 @@
         </is>
       </c>
       <c r="AY371" t="inlineStr"/>
+      <c r="AZ371" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111783209</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
@@ -41849,6 +43704,11 @@
         </is>
       </c>
       <c r="AY372" t="inlineStr"/>
+      <c r="AZ372" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127029778</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
@@ -41955,6 +43815,11 @@
         </is>
       </c>
       <c r="AY373" t="inlineStr"/>
+      <c r="AZ373" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127784893</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
@@ -42061,6 +43926,11 @@
         </is>
       </c>
       <c r="AY374" t="inlineStr"/>
+      <c r="AZ374" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127784894</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
@@ -42177,6 +44047,11 @@
         </is>
       </c>
       <c r="AY375" t="inlineStr"/>
+      <c r="AZ375" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127784987</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
@@ -42284,6 +44159,11 @@
         </is>
       </c>
       <c r="AY376" t="inlineStr"/>
+      <c r="AZ376" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127013784</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
@@ -42381,6 +44261,11 @@
         </is>
       </c>
       <c r="AY377" t="inlineStr"/>
+      <c r="AZ377" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127085229</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
@@ -42478,6 +44363,11 @@
         </is>
       </c>
       <c r="AY378" t="inlineStr"/>
+      <c r="AZ378" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127085230</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
@@ -42586,6 +44476,11 @@
         </is>
       </c>
       <c r="AY379" t="inlineStr"/>
+      <c r="AZ379" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111966750</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
@@ -42694,6 +44589,11 @@
         </is>
       </c>
       <c r="AY380" t="inlineStr"/>
+      <c r="AZ380" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110253973</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
@@ -42815,6 +44715,11 @@
         </is>
       </c>
       <c r="AY381" t="inlineStr"/>
+      <c r="AZ381" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134453125</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
@@ -42939,6 +44844,11 @@
         </is>
       </c>
       <c r="AY382" t="inlineStr"/>
+      <c r="AZ382" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127158796</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
@@ -43036,8 +44946,397 @@
         </is>
       </c>
       <c r="AY383" t="inlineStr"/>
+      <c r="AZ383" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127784892</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ233" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ234" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ235" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ236" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ237" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ238" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ239" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ240" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ241" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ242" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ243" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ244" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ245" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ246" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ247" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ248" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ249" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ250" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ251" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ252" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ253" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ254" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ255" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ256" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ257" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ258" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ259" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ260" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ261" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ262" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ263" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ264" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ265" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ266" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ267" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ268" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ269" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ270" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ271" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ272" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ273" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ274" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ275" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ276" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ277" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ278" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ279" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ280" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ281" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ282" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ283" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ284" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ285" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ286" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ287" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ288" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ289" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ290" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ291" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ292" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ293" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ294" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ295" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ296" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ297" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ298" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ299" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ300" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ301" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ302" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ303" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ304" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ305" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ306" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ307" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ308" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ309" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ310" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ311" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ312" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ313" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ314" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ315" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ316" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ317" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ318" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ319" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ320" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ321" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ322" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ323" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ324" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ325" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ326" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ327" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ328" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ329" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ330" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ331" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ332" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ333" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ334" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ335" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ336" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ337" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ338" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ339" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ340" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ341" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ342" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ343" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ344" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ345" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ346" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ347" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ348" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ349" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ350" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ351" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ352" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ353" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ354" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ355" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ356" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ357" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ358" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ359" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ360" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ361" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ362" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ363" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ364" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ365" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ366" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ367" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ368" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ369" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ370" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ371" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ372" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ373" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ374" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ375" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ376" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ377" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ378" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ379" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ380" r:id="rId379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ381" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ382" r:id="rId381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ383" r:id="rId382"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>